--- a/事業計画_Ver0.8.xlsx
+++ b/事業計画_Ver0.8.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資本政策とリターン" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業界ベンチマーク" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出所と仮置き" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="知財" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="知財・法規制・リスク" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改訂履歴" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
@@ -5829,7 +5829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5841,14 +5841,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>知財 — 支払う側と、取る側</t>
+          <t>知財・法規制・リスク</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AI映像は「他人の権利を使って作り、自分の権利を積む」事業。両方を1枚で持つ。</t>
+          <t>他人の権利を使って作り、自分の権利を積む事業。払う側・取る側・守る側を1枚で持つ。</t>
         </is>
       </c>
     </row>
@@ -6249,6 +6249,169 @@
       <c r="A34" s="38" t="inlineStr">
         <is>
           <t>★ 金額はいずれも仮置き。弁理士の見積を取っていない。出願を1件でなく複数に分けると初期費用は上振れする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>④ 法規制 — 1年目に確定させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>いつ</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>中身</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>なぜ効くか</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="48" t="inlineStr">
+        <is>
+          <t>★ 資金決済法上の位置づけ</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1年目に弁護士と確認</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>③の仲介が収納代行で済むか、資金移動業の登録が必要か</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>登録が要るなら供託・体制整備・監督が乗り、③の設計そのものが変わる。最重要論点</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>データの越境</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1年目</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>中国のデータ越境規制と、日本の個人情報保護法への対応</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>①③とも日本の発注者の素材が中国へ渡る。越境移転の同意取得と委託先管理が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>業務委託契約</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1年目に雛形を作成</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>偽装請負と読まれない設計（指揮命令をしない／成果物単位で発注する）</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>制作ディレクション・ベトナム開発・中国クリエイターの全てが業務委託。上場審査で必ず見られる</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>⑤ リスク — ③では一次責任が当社に来る</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>リスク</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>中身</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>生成物の類似性</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr"/>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>生成AIの出力が既存作品に似る。学習元をたどれないため事前検証に限界がある</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>★賠償責任保険の付保。工程ツールに類似チェックを組み込み、検収前に走らせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>肖像・声の権利</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr"/>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>実在人物に似た顔・声が出る。③は発注者とクリエイターの間で素材が動く</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>★契約書で責任上限を設定（当社が受領した手数料額を上限とする等）。素材の権利表明を発注者に求める</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="38" t="inlineStr">
+        <is>
+          <t>⚠ ③は当社が場を提供する以上、権利侵害の申立ては一次的に当社へ来る。クリエイター任せにはできない。保険の料率と填補範囲、責任上限の水準はいずれも★仮置きで、1年目に弁護士および保険代理店と確定させる。</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6642,15 +6805,57 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr"/>
+      <c r="B25" s="53" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>知財シートを「知財・法規制・リスク」に拡張（法規制3項目・リスク2項目を追加）</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>資金決済法の位置づけ／データ越境／偽装請負／生成物の類似性／肖像・声の権利</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr"/>
+      <c r="B26" s="53" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>デッキ19枚目を「知財・法規制・リスク」1枚に集約（28枚のまま）</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>枚数を増やさないため、知財単独スライドを作り替えた</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr"/>
+      <c r="B27" s="53" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>③の価格前提を「次版で中点成約に変更」と記述（数値は未変更）</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>⚠ この段階では損益計算書・資金計画の数値を一切変更していない。数値改訂は次版</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>⚠ 0.4 → 0.5 は構造の作り直し、0.5 → 0.6 は前提を実勢データで詰めたもの、0.7 は③-Cの件数を落として120億に合わせ、0.8 は知財を明示して前提を保守化したもの。5期の売上は 88.1億 → 130.3億 → 120.0億、社員は 61名 → 22名。数字が良くなった分だけ、前提の説明責任が重くなっている。</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="38" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>⚠ PPTX「投資家向け企画書 Ver1.4.pptx」はまだ旧番号のまま。改番するかは松田さんの指示待ち。</t>
         </is>

--- a/事業計画_Ver0.8.xlsx
+++ b/事業計画_Ver0.8.xlsx
@@ -139,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -245,8 +245,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -2699,23 +2702,23 @@
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr"/>
-      <c r="C33" s="46">
+      <c r="C33" s="47">
         <f>SUM(C21:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="46">
+      <c r="D33" s="47">
         <f>SUM(D21:D32)</f>
         <v/>
       </c>
-      <c r="E33" s="46">
+      <c r="E33" s="47">
         <f>SUM(E21:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="46">
+      <c r="F33" s="47">
         <f>SUM(F21:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="46">
+      <c r="G33" s="47">
         <f>SUM(G21:G32)</f>
         <v/>
       </c>
@@ -2755,23 +2758,23 @@
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="47">
+      <c r="C35" s="48">
         <f>IF(C12=0,0,C34/C12)</f>
         <v/>
       </c>
-      <c r="D35" s="47">
+      <c r="D35" s="48">
         <f>IF(D12=0,0,D34/D12)</f>
         <v/>
       </c>
-      <c r="E35" s="47">
+      <c r="E35" s="48">
         <f>IF(E12=0,0,E34/E12)</f>
         <v/>
       </c>
-      <c r="F35" s="47">
+      <c r="F35" s="48">
         <f>IF(F12=0,0,F34/F12)</f>
         <v/>
       </c>
-      <c r="G35" s="47">
+      <c r="G35" s="48">
         <f>IF(G12=0,0,G34/G12)</f>
         <v/>
       </c>
@@ -3054,23 +3057,23 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="46">
+      <c r="C4" s="47">
         <f>'損益計算書'!C34</f>
         <v/>
       </c>
-      <c r="D4" s="46">
+      <c r="D4" s="47">
         <f>'損益計算書'!D34</f>
         <v/>
       </c>
-      <c r="E4" s="46">
+      <c r="E4" s="47">
         <f>'損益計算書'!E34</f>
         <v/>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="47">
         <f>'損益計算書'!F34</f>
         <v/>
       </c>
-      <c r="G4" s="46">
+      <c r="G4" s="47">
         <f>'損益計算書'!G34</f>
         <v/>
       </c>
@@ -3242,23 +3245,23 @@
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="46">
+      <c r="C11" s="47">
         <f>C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="47">
         <f>D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="47">
         <f>E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="47">
         <f>F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="47">
         <f>G9+G10</f>
         <v/>
       </c>
@@ -3443,23 +3446,23 @@
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="46">
+      <c r="C19" s="47">
         <f>C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="46">
+      <c r="D19" s="47">
         <f>D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="47">
         <f>E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="46">
+      <c r="F19" s="47">
         <f>F16+F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="46">
+      <c r="G19" s="47">
         <f>G16+G17+G18</f>
         <v/>
       </c>
@@ -3471,23 +3474,23 @@
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="46">
+      <c r="C21" s="47">
         <f>C14+C15+C19</f>
         <v/>
       </c>
-      <c r="D21" s="46">
+      <c r="D21" s="47">
         <f>D14+D15+D19</f>
         <v/>
       </c>
-      <c r="E21" s="46">
+      <c r="E21" s="47">
         <f>E14+E15+E19</f>
         <v/>
       </c>
-      <c r="F21" s="46">
+      <c r="F21" s="47">
         <f>F14+F15+F19</f>
         <v/>
       </c>
-      <c r="G21" s="46">
+      <c r="G21" s="47">
         <f>G14+G15+G19</f>
         <v/>
       </c>
@@ -4185,7 +4188,7 @@
           <t>転換時のシード持分</t>
         </is>
       </c>
-      <c r="C15" s="45">
+      <c r="C15" s="46">
         <f>C7/C6</f>
         <v/>
       </c>
@@ -4201,7 +4204,7 @@
           <t>シリーズA の持分</t>
         </is>
       </c>
-      <c r="C16" s="45">
+      <c r="C16" s="46">
         <f>C10/C9</f>
         <v/>
       </c>
@@ -4281,7 +4284,7 @@
           <t>設立（資本金800万）</t>
         </is>
       </c>
-      <c r="C20" s="48" t="inlineStr">
+      <c r="C20" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4326,7 +4329,7 @@
           <t>ESOP枠を設計</t>
         </is>
       </c>
-      <c r="C21" s="48" t="inlineStr">
+      <c r="C21" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4371,7 +4374,7 @@
           <t>J-KISS 発行（未転換）</t>
         </is>
       </c>
-      <c r="C22" s="48" t="inlineStr">
+      <c r="C22" s="49" t="inlineStr">
         <is>
           <t>1.42億</t>
         </is>
@@ -4416,7 +4419,7 @@
           <t>シリーズA ＋ J-KISS転換</t>
         </is>
       </c>
-      <c r="C23" s="48" t="inlineStr">
+      <c r="C23" s="49" t="inlineStr">
         <is>
           <t>3億</t>
         </is>
@@ -4461,7 +4464,7 @@
           <t>ESOP補充</t>
         </is>
       </c>
-      <c r="C24" s="48" t="inlineStr">
+      <c r="C24" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4506,7 +4509,7 @@
           <t>IPO 公募</t>
         </is>
       </c>
-      <c r="C25" s="48" t="inlineStr">
+      <c r="C25" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4551,7 +4554,7 @@
           <t>売出し（既存株主が売る）</t>
         </is>
       </c>
-      <c r="C26" s="48" t="inlineStr">
+      <c r="C26" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4634,7 +4637,7 @@
           <t>創業者（役員）</t>
         </is>
       </c>
-      <c r="B30" s="47">
+      <c r="B30" s="48">
         <f>D26</f>
         <v/>
       </c>
@@ -4648,7 +4651,7 @@
           <t>× 除外</t>
         </is>
       </c>
-      <c r="E30" s="47" t="n">
+      <c r="E30" s="48" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="7" t="inlineStr">
@@ -4663,7 +4666,7 @@
           <t>ESOP枠</t>
         </is>
       </c>
-      <c r="B31" s="47">
+      <c r="B31" s="48">
         <f>E26</f>
         <v/>
       </c>
@@ -4677,7 +4680,7 @@
           <t>× 除外</t>
         </is>
       </c>
-      <c r="E31" s="47" t="n">
+      <c r="E31" s="48" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
@@ -4692,7 +4695,7 @@
           <t>シード投資家 保有分</t>
         </is>
       </c>
-      <c r="B32" s="47">
+      <c r="B32" s="48">
         <f>F26</f>
         <v/>
       </c>
@@ -4704,7 +4707,7 @@
         <f>IF(B32&lt;0.1,"○ 算入","× 除外")</f>
         <v/>
       </c>
-      <c r="E32" s="47">
+      <c r="E32" s="48">
         <f>IF(B32&lt;0.1,B32,0)</f>
         <v/>
       </c>
@@ -4720,7 +4723,7 @@
           <t>シリーズA 保有分</t>
         </is>
       </c>
-      <c r="B33" s="47">
+      <c r="B33" s="48">
         <f>G26</f>
         <v/>
       </c>
@@ -4732,7 +4735,7 @@
         <f>IF(B33&lt;0.1,"○ 算入","× 除外")</f>
         <v/>
       </c>
-      <c r="E33" s="47">
+      <c r="E33" s="48">
         <f>IF(B33&lt;0.1,B33,0)</f>
         <v/>
       </c>
@@ -4748,7 +4751,7 @@
           <t>公募・売出し</t>
         </is>
       </c>
-      <c r="B34" s="47">
+      <c r="B34" s="48">
         <f>H26</f>
         <v/>
       </c>
@@ -4762,7 +4765,7 @@
           <t>○ 算入</t>
         </is>
       </c>
-      <c r="E34" s="47">
+      <c r="E34" s="48">
         <f>B34</f>
         <v/>
       </c>
@@ -4793,7 +4796,7 @@
         <f>IF(E35&gt;=0.25,"○ 満たす","× 不足")</f>
         <v/>
       </c>
-      <c r="E36" s="49">
+      <c r="E36" s="50">
         <f>E35-0.25</f>
         <v/>
       </c>
@@ -4929,7 +4932,7 @@
           <t>転換時のシード持分</t>
         </is>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="46">
         <f>'資本構成の推移'!C15</f>
         <v/>
       </c>
@@ -4955,7 +4958,7 @@
           <t>転換後の希薄化</t>
         </is>
       </c>
-      <c r="B7" s="50">
+      <c r="B7" s="51">
         <f>B8/B6</f>
         <v/>
       </c>
@@ -4981,7 +4984,7 @@
           <t>上場後のシード持分</t>
         </is>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="46">
         <f>'資本構成の推移'!F25</f>
         <v/>
       </c>
@@ -5103,7 +5106,7 @@
         <f>E13*$B$8</f>
         <v/>
       </c>
-      <c r="G13" s="51">
+      <c r="G13" s="52">
         <f>F13/$B$5</f>
         <v/>
       </c>
@@ -5140,7 +5143,7 @@
         <f>E14*$B$8</f>
         <v/>
       </c>
-      <c r="G14" s="51">
+      <c r="G14" s="52">
         <f>F14/$B$5</f>
         <v/>
       </c>
@@ -5173,7 +5176,7 @@
         <f>E15*$B$8</f>
         <v/>
       </c>
-      <c r="G15" s="51">
+      <c r="G15" s="52">
         <f>F15/$B$5</f>
         <v/>
       </c>
@@ -5250,7 +5253,7 @@
         <f>E19*$B$8</f>
         <v/>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="52">
         <f>F19/$B$5</f>
         <v/>
       </c>
@@ -5281,7 +5284,7 @@
         <f>E20*$B$8</f>
         <v/>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="52">
         <f>F20/$B$5</f>
         <v/>
       </c>
@@ -5551,7 +5554,7 @@
           <t>Runway</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>非開示</t>
         </is>
@@ -5578,7 +5581,7 @@
           <t>Technicolor</t>
         </is>
       </c>
-      <c r="B13" s="48" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>非開示</t>
         </is>
@@ -5605,7 +5608,7 @@
           <t>【当社 5期（2031年）】</t>
         </is>
       </c>
-      <c r="B14" s="52">
+      <c r="B14" s="53">
         <f>'損益計算書'!$G$12/100</f>
         <v/>
       </c>
@@ -5699,12 +5702,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>── 実測 ──</t>
         </is>
       </c>
-      <c r="B4" s="48" t="inlineStr"/>
+      <c r="B4" s="49" t="inlineStr"/>
       <c r="C4" s="20" t="inlineStr"/>
       <c r="D4" s="7" t="inlineStr"/>
     </row>
@@ -5714,7 +5717,7 @@
           <t>国内 映像制作市場</t>
         </is>
       </c>
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>4,580億円</t>
         </is>
@@ -5736,7 +5739,7 @@
           <t>インターネット広告制作費</t>
         </is>
       </c>
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>4,922億円</t>
         </is>
@@ -5758,7 +5761,7 @@
           <t>法人数</t>
         </is>
       </c>
-      <c r="B7" s="48" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>295万6,717社</t>
         </is>
@@ -5780,7 +5783,7 @@
           <t>中国 剪辑師 平均月給</t>
         </is>
       </c>
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>8,935元</t>
         </is>
@@ -5802,7 +5805,7 @@
           <t>中国 微短劇 直接就業者</t>
         </is>
       </c>
-      <c r="B9" s="48" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>約69万人</t>
         </is>
@@ -5824,7 +5827,7 @@
           <t>Stripe 決済手数料</t>
         </is>
       </c>
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>国内カード3.6%／銀行振込1.5%</t>
         </is>
@@ -5846,7 +5849,7 @@
           <t>S3 Standard 東京</t>
         </is>
       </c>
-      <c r="B11" s="48" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>1TB/月 ≈ $25</t>
         </is>
@@ -5868,7 +5871,7 @@
           <t>CloudFront 東京</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>$0.085/GB</t>
         </is>
@@ -5890,7 +5893,7 @@
           <t>ベンチマーク各社の売上</t>
         </is>
       </c>
-      <c r="B13" s="48" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>業界ベンチマーク シート</t>
         </is>
@@ -5912,7 +5915,7 @@
           <t>東証グロース 上場維持基準</t>
         </is>
       </c>
-      <c r="B14" s="48" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>5年経過後 時価総額100億円</t>
         </is>
@@ -5929,12 +5932,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="53" t="inlineStr">
+      <c r="A15" s="54" t="inlineStr">
         <is>
           <t>── 確認できなかった ──</t>
         </is>
       </c>
-      <c r="B15" s="48" t="inlineStr"/>
+      <c r="B15" s="49" t="inlineStr"/>
       <c r="C15" s="20" t="inlineStr"/>
       <c r="D15" s="7" t="inlineStr"/>
     </row>
@@ -5944,7 +5947,7 @@
           <t>スキルシェア市場の映像比率</t>
         </is>
       </c>
-      <c r="B16" s="48" t="inlineStr">
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>非公表</t>
         </is>
@@ -5961,12 +5964,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="A17" s="54" t="inlineStr">
         <is>
           <t>── 松田さんの決定 ──</t>
         </is>
       </c>
-      <c r="B17" s="48" t="inlineStr"/>
+      <c r="B17" s="49" t="inlineStr"/>
       <c r="C17" s="20" t="inlineStr"/>
       <c r="D17" s="7" t="inlineStr"/>
     </row>
@@ -5976,7 +5979,7 @@
           <t>③ 手数料率</t>
         </is>
       </c>
-      <c r="B18" s="48" t="inlineStr">
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>一律30%（クリエイター70%）</t>
         </is>
@@ -5998,7 +6001,7 @@
           <t>③ 送金・為替</t>
         </is>
       </c>
-      <c r="B19" s="48" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -6020,7 +6023,7 @@
           <t>③ 成約位置</t>
         </is>
       </c>
-      <c r="B20" s="48" t="inlineStr">
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>均等（価格帯の中点）</t>
         </is>
@@ -6042,7 +6045,7 @@
           <t>① クリエイター支払</t>
         </is>
       </c>
-      <c r="B21" s="48" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>厚いまま（実効時給3,000〜6,000円）</t>
         </is>
@@ -6064,7 +6067,7 @@
           <t>②-C セルフサーブ</t>
         </is>
       </c>
-      <c r="B22" s="48" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>②に置く／用途特化</t>
         </is>
@@ -6081,12 +6084,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="53" t="inlineStr">
+      <c r="A23" s="54" t="inlineStr">
         <is>
           <t>── ★私が置いた値 ──</t>
         </is>
       </c>
-      <c r="B23" s="48" t="inlineStr"/>
+      <c r="B23" s="49" t="inlineStr"/>
       <c r="C23" s="20" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr"/>
     </row>
@@ -6096,7 +6099,7 @@
           <t>AX倍率</t>
         </is>
       </c>
-      <c r="B24" s="48" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>1.0 → 4.0倍</t>
         </is>
@@ -6118,7 +6121,7 @@
           <t>① 商品の値引率</t>
         </is>
       </c>
-      <c r="B25" s="48" t="inlineStr">
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>一律50%</t>
         </is>
@@ -6140,7 +6143,7 @@
           <t>① 難度係数</t>
         </is>
       </c>
-      <c r="B26" s="48" t="inlineStr">
+      <c r="B26" s="49" t="inlineStr">
         <is>
           <t>3.0 / 1.8 / 1.0 / 0.8</t>
         </is>
@@ -6162,7 +6165,7 @@
           <t>① 商品構成比</t>
         </is>
       </c>
-      <c r="B27" s="48" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>年を追って上位帯へシフト</t>
         </is>
@@ -6184,7 +6187,7 @@
           <t>① 営業の担当社数・リピート</t>
         </is>
       </c>
-      <c r="B28" s="48" t="inlineStr">
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>40社／年6本</t>
         </is>
@@ -6206,7 +6209,7 @@
           <t>② SKU単価・席数・Ent比率</t>
         </is>
       </c>
-      <c r="B29" s="48" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>商品マスタ② 参照</t>
         </is>
@@ -6228,7 +6231,7 @@
           <t>③ 工数・上限価格・件数</t>
         </is>
       </c>
-      <c r="B30" s="48" t="inlineStr">
+      <c r="B30" s="49" t="inlineStr">
         <is>
           <t>商品マスタ③ 参照</t>
         </is>
@@ -6250,7 +6253,7 @@
           <t>③ システム原価の内訳</t>
         </is>
       </c>
-      <c r="B31" s="48" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>尺・保管期間・トークン数</t>
         </is>
@@ -6272,7 +6275,7 @@
           <t>希薄化係数</t>
         </is>
       </c>
-      <c r="B32" s="48" t="inlineStr">
+      <c r="B32" s="49" t="inlineStr">
         <is>
           <t>資本構成の推移 参照</t>
         </is>
@@ -6289,12 +6292,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="53" t="inlineStr">
+      <c r="A33" s="54" t="inlineStr">
         <is>
           <t>── 未確定 ──</t>
         </is>
       </c>
-      <c r="B33" s="48" t="inlineStr"/>
+      <c r="B33" s="49" t="inlineStr"/>
       <c r="C33" s="20" t="inlineStr"/>
       <c r="D33" s="7" t="inlineStr"/>
     </row>
@@ -6304,7 +6307,7 @@
           <t>中国の映像制作パートナー</t>
         </is>
       </c>
-      <c r="B34" s="48" t="inlineStr">
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>社名 ［記入予定］</t>
         </is>
@@ -6326,7 +6329,7 @@
           <t>パートナーの取り分</t>
         </is>
       </c>
-      <c r="B35" s="48" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>30%側か70%側か</t>
         </is>
@@ -6348,7 +6351,7 @@
           <t>業務委託の契約設計</t>
         </is>
       </c>
-      <c r="B36" s="48" t="inlineStr">
+      <c r="B36" s="49" t="inlineStr">
         <is>
           <t>─</t>
         </is>
@@ -6712,7 +6715,7 @@
           <t>1期</t>
         </is>
       </c>
-      <c r="B28" s="54" t="inlineStr">
+      <c r="B28" s="55" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -6729,7 +6732,7 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="B29" s="54" t="inlineStr">
+      <c r="B29" s="55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -6746,7 +6749,7 @@
           <t>3期</t>
         </is>
       </c>
-      <c r="B30" s="54" t="inlineStr">
+      <c r="B30" s="55" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -6763,7 +6766,7 @@
           <t>4期</t>
         </is>
       </c>
-      <c r="B31" s="54" t="inlineStr">
+      <c r="B31" s="55" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -6780,7 +6783,7 @@
           <t>5期</t>
         </is>
       </c>
-      <c r="B32" s="54" t="inlineStr">
+      <c r="B32" s="55" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -7018,12 +7021,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" s="56" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="57" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -7041,7 +7044,7 @@
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr"/>
-      <c r="B5" s="56" t="inlineStr"/>
+      <c r="B5" s="57" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>市場規模の次に「業界の売上」を新設</t>
@@ -7054,12 +7057,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="B6" s="56" t="inlineStr">
+      <c r="B6" s="57" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -7077,7 +7080,7 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr"/>
-      <c r="B7" s="56" t="inlineStr"/>
+      <c r="B7" s="57" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>① 単価を「企業の現行支払×50%」に。本数は営業体制から</t>
@@ -7091,7 +7094,7 @@
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr"/>
-      <c r="B8" s="56" t="inlineStr"/>
+      <c r="B8" s="57" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>② 5SKU・法人2階建て・②-Cセルフサーブを新設</t>
@@ -7105,7 +7108,7 @@
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr"/>
-      <c r="B9" s="56" t="inlineStr"/>
+      <c r="B9" s="57" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
           <t>③ 14商品。下限はクリエイターの留保価格、上限は日本の支払意思</t>
@@ -7118,12 +7121,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="B10" s="56" t="inlineStr">
+      <c r="B10" s="57" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -7141,7 +7144,7 @@
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr"/>
-      <c r="B11" s="56" t="inlineStr"/>
+      <c r="B11" s="57" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
           <t>③ 手数料を一律30%に。30%から決済・送金・システム原価を引く</t>
@@ -7155,7 +7158,7 @@
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr"/>
-      <c r="B12" s="56" t="inlineStr"/>
+      <c r="B12" s="57" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>③ システム原価を商品別に積み上げ（120円→53円）</t>
@@ -7169,7 +7172,7 @@
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr"/>
-      <c r="B13" s="56" t="inlineStr"/>
+      <c r="B13" s="57" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>② ACVとARRを分離。①③のARRはゼロと明示</t>
@@ -7183,7 +7186,7 @@
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr"/>
-      <c r="B14" s="56" t="inlineStr"/>
+      <c r="B14" s="57" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
           <t>エンジニアを社員40名 → PM4名＋ベトナム委託19名</t>
@@ -7197,7 +7200,7 @@
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr"/>
-      <c r="B15" s="56" t="inlineStr"/>
+      <c r="B15" s="57" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
           <t>エンジニアにもAX倍率（5期2.2倍）</t>
@@ -7211,7 +7214,7 @@
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr"/>
-      <c r="B16" s="56" t="inlineStr"/>
+      <c r="B16" s="57" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>中国・東欧・ロシアを委託先から外す</t>
@@ -7225,7 +7228,7 @@
     </row>
     <row r="17">
       <c r="A17" s="20" t="inlineStr"/>
-      <c r="B17" s="56" t="inlineStr"/>
+      <c r="B17" s="57" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
           <t>中国クリエイターの登録数を採用計画（入力）に。1期30名</t>
@@ -7239,7 +7242,7 @@
     </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr"/>
-      <c r="B18" s="56" t="inlineStr"/>
+      <c r="B18" s="57" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>③ の価格を中点から上限に</t>
@@ -7253,7 +7256,7 @@
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr"/>
-      <c r="B19" s="56" t="inlineStr"/>
+      <c r="B19" s="57" t="inlineStr"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>管理・コーポレートを6名→3名</t>
@@ -7266,12 +7269,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="B20" s="56" t="inlineStr">
+      <c r="B20" s="57" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -7289,7 +7292,7 @@
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr"/>
-      <c r="B21" s="56" t="inlineStr"/>
+      <c r="B21" s="57" t="inlineStr"/>
       <c r="C21" s="5" t="inlineStr">
         <is>
           <t>版番号を繰り下げ（1.x → 0.x）</t>
@@ -7302,12 +7305,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="55" t="inlineStr">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="B22" s="56" t="inlineStr">
+      <c r="B22" s="57" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -7325,7 +7328,7 @@
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr"/>
-      <c r="B23" s="56" t="inlineStr"/>
+      <c r="B23" s="57" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
           <t>知財関連費を新設（1期300万★／2期以降 売上の0.5%★）</t>
@@ -7339,7 +7342,7 @@
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr"/>
-      <c r="B24" s="56" t="inlineStr"/>
+      <c r="B24" s="57" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
           <t>AX倍率を「実測して更新する指標」と明記</t>
@@ -7353,7 +7356,7 @@
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr"/>
-      <c r="B25" s="56" t="inlineStr"/>
+      <c r="B25" s="57" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
           <t>知財シートを「知財・法規制・リスク」に拡張（法規制3項目・リスク2項目を追加）</t>
@@ -7367,7 +7370,7 @@
     </row>
     <row r="26">
       <c r="A26" s="20" t="inlineStr"/>
-      <c r="B26" s="56" t="inlineStr"/>
+      <c r="B26" s="57" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>デッキ19枚目を「知財・法規制・リスク」1枚に集約（28枚のまま）</t>
@@ -7381,7 +7384,7 @@
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr"/>
-      <c r="B27" s="56" t="inlineStr"/>
+      <c r="B27" s="57" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>③の価格前提を「次版で中点成約に変更」と記述（数値は未変更）</t>
@@ -7394,44 +7397,44 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="55" t="inlineStr">
+      <c r="A28" s="56" t="inlineStr">
         <is>
           <t>0.8 数値改訂</t>
         </is>
       </c>
-      <c r="B28" s="56" t="inlineStr">
+      <c r="B28" s="57" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>③ 上限成約 → 中点成約</t>
+          <t>③ 価格を ToC＝上限／ToB＝中点 に分ける</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>5期GMV 142.5億→83.4億（約59%）。③売上 42.7億→25.0億。上限成約は上振れシナリオとして保持</t>
+          <t>ToC（個人向け6商品＋個人オーダー）は定価で交渉が入らない。ToB（中小企業6商品＋企業オーダー）は相見積もりと交渉が入るので上限に張り付かない。5期GMV 142.5億→91.8億</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr"/>
-      <c r="B29" s="56" t="inlineStr"/>
+      <c r="B29" s="57" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>② に解約率を新設（★法人 年10%／個人 年40%）</t>
+          <t>② に解約率を新設（★法人・個人とも 年30%）</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>契約数は「新規獲得−解約」の純増に。法人600→558社、個人17,000→13,320人。②売上 41.6億→35.8億</t>
+          <t>契約数は「新規獲得−解約」の純増に。法人600→481社、個人17,000→14,180人。②売上 41.6億→34.3億</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr"/>
-      <c r="B30" s="56" t="inlineStr"/>
+      <c r="B30" s="57" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>②の解約が①にも波及</t>
@@ -7445,7 +7448,7 @@
     </row>
     <row r="31">
       <c r="A31" s="20" t="inlineStr"/>
-      <c r="B31" s="56" t="inlineStr"/>
+      <c r="B31" s="57" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>貸倒引当を新設（★売上の0.5%）</t>
@@ -7459,7 +7462,7 @@
     </row>
     <row r="32">
       <c r="A32" s="20" t="inlineStr"/>
-      <c r="B32" s="56" t="inlineStr"/>
+      <c r="B32" s="57" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>採用費を新設（★4人目から・想定年収の30%）</t>
@@ -7473,7 +7476,7 @@
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr"/>
-      <c r="B33" s="56" t="inlineStr"/>
+      <c r="B33" s="57" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>監査法人費用を新設（★3期から年2,000万）</t>
@@ -7487,7 +7490,7 @@
     </row>
     <row r="34">
       <c r="A34" s="20" t="inlineStr"/>
-      <c r="B34" s="56" t="inlineStr"/>
+      <c r="B34" s="57" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>上場関連費用を新設（★上場期に1億）</t>
@@ -7501,7 +7504,7 @@
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr"/>
-      <c r="B35" s="56" t="inlineStr"/>
+      <c r="B35" s="57" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>設備投資ゼロの前提を見直し（★1期2／3期6／4期12百万）</t>
@@ -7515,7 +7518,7 @@
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr"/>
-      <c r="B36" s="56" t="inlineStr"/>
+      <c r="B36" s="57" t="inlineStr"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>為替感応度を追加（資金計画シート）</t>
@@ -7529,7 +7532,7 @@
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr"/>
-      <c r="B37" s="56" t="inlineStr"/>
+      <c r="B37" s="57" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>再計算の結果</t>
@@ -7537,7 +7540,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>5期 売上 120.0→95.6億、営業利益 45.4→26.3億（37.8%→27.6%）。黒字化は3期のまま。2期末キャッシュ188百万でシリーズA前の資金ショートなし</t>
+          <t>5期 売上 120.0→94.9億、営業利益 45.4→26.4億（37.8%→27.8%）。黒字化は3期のまま。2期末キャッシュ198百万でシリーズA前の資金ショートなし</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8997,7 @@
         </is>
       </c>
       <c r="B15" s="27">
-        <f>'商品マスタ③'!$I$23</f>
+        <f>'商品マスタ③'!$K$23</f>
         <v/>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -11625,20 +11628,20 @@
         <v>0</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>★年10%。工程に組み込まれるので粘着性は高いが、B2B SaaSの標準的な水準を置く</t>
+          <t>★年30%（松田さん指示）。B2B SaaSの一般水準（5〜15%）より高く、保守側に置いている</t>
         </is>
       </c>
     </row>
@@ -11862,20 +11865,20 @@
         <v>0</v>
       </c>
       <c r="D28" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E28" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F28" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G28" s="23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>★年40%（月4%相当）。個人向けSaaSは解約が早い。法人の4倍で置く</t>
+          <t>★年30%（松田さん指示）。個人向けSaaSとしてはむしろ低め。法人と同率で置いている</t>
         </is>
       </c>
     </row>
@@ -12448,20 +12451,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12474,7 +12479,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>価格は上限を採用（松田さんの決定）。上限＝日本の発注者の支払意思。下限はクリエイターの留保価格で、下回ると供給が付かないという床。中点は参考。</t>
+          <t>ToC（個人向け）は上限＝定価で成約。ToB（中小企業・企業オーダー）は交渉が入るので中点で成約。下限はクリエイターの留保価格で、下回ると供給が付かないという床。</t>
         </is>
       </c>
     </row>
@@ -12491,45 +12496,55 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>参考 軽い場合</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>標準工数</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>下限（供給）</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>上限（上振れ）</t>
-        </is>
-      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>中点＝採用価格</t>
+          <t>上限（需要）</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>中点</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>採用価格</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>5期件数</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>年間工数</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>5期GMV(百万)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>上限の根拠</t>
         </is>
@@ -12546,35 +12561,44 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>ToC</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="E5" s="29" t="n">
         <v>1.5</v>
       </c>
-      <c r="E5" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D5/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F5" s="41" t="n">
+      <c r="F5" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E5/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G5" s="22" t="n">
         <v>10000</v>
       </c>
-      <c r="G5" s="6">
-        <f>(E5+F5)/2</f>
-        <v/>
-      </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="13">
+        <f>(F5+G5)/2</f>
+        <v/>
+      </c>
+      <c r="I5" s="6">
+        <f>IF($C5="ToC",G5,H5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="22" t="n">
         <v>25000</v>
       </c>
-      <c r="I5" s="8">
-        <f>D5*H5</f>
-        <v/>
-      </c>
-      <c r="J5" s="33">
-        <f>G5*H5/1000000</f>
-        <v/>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="8">
+        <f>E5*J5</f>
+        <v/>
+      </c>
+      <c r="L5" s="33">
+        <f>I5*J5/1000000</f>
+        <v/>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>個人の動画編集外注 5千〜3万の下側</t>
         </is>
@@ -12591,35 +12615,44 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>ToC</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="E6" s="29" t="n">
         <v>2.5</v>
       </c>
-      <c r="E6" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D6/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F6" s="41" t="n">
+      <c r="F6" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E6/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G6" s="22" t="n">
         <v>15000</v>
       </c>
-      <c r="G6" s="6">
-        <f>(E6+F6)/2</f>
-        <v/>
-      </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="13">
+        <f>(F6+G6)/2</f>
+        <v/>
+      </c>
+      <c r="I6" s="6">
+        <f>IF($C6="ToC",G6,H6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="I6" s="8">
-        <f>D6*H6</f>
-        <v/>
-      </c>
-      <c r="J6" s="33">
-        <f>G6*H6/1000000</f>
-        <v/>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="K6" s="8">
+        <f>E6*J6</f>
+        <v/>
+      </c>
+      <c r="L6" s="33">
+        <f>I6*J6/1000000</f>
+        <v/>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>サプライズ動画 数千〜2万</t>
         </is>
@@ -12636,35 +12669,44 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>ToC</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="E7" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D7/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F7" s="41" t="n">
+      <c r="F7" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E7/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G7" s="22" t="n">
         <v>18000</v>
       </c>
-      <c r="G7" s="6">
-        <f>(E7+F7)/2</f>
-        <v/>
-      </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="13">
+        <f>(F7+G7)/2</f>
+        <v/>
+      </c>
+      <c r="I7" s="6">
+        <f>IF($C7="ToC",G7,H7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="22" t="n">
         <v>8000</v>
       </c>
-      <c r="I7" s="8">
-        <f>D7*H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="33">
-        <f>G7*H7/1000000</f>
-        <v/>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="8">
+        <f>E7*J7</f>
+        <v/>
+      </c>
+      <c r="L7" s="33">
+        <f>I7*J7/1000000</f>
+        <v/>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>還暦・退職。誕生日より重い</t>
         </is>
@@ -12681,35 +12723,44 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>ToC</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="E8" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D8/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E8/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G8" s="22" t="n">
         <v>30000</v>
       </c>
-      <c r="G8" s="6">
-        <f>(E8+F8)/2</f>
-        <v/>
-      </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="13">
+        <f>(F8+G8)/2</f>
+        <v/>
+      </c>
+      <c r="I8" s="6">
+        <f>IF($C8="ToC",G8,H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="22" t="n">
         <v>10000</v>
       </c>
-      <c r="I8" s="8">
-        <f>D8*H8</f>
-        <v/>
-      </c>
-      <c r="J8" s="33">
-        <f>G8*H8/1000000</f>
-        <v/>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="K8" s="8">
+        <f>E8*J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="33">
+        <f>I8*J8/1000000</f>
+        <v/>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
         <is>
           <t>二次会・余興 1〜5万</t>
         </is>
@@ -12726,35 +12777,44 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>ToC</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="E9" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D9/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F9" s="41" t="n">
+      <c r="F9" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E9/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G9" s="22" t="n">
         <v>50000</v>
       </c>
-      <c r="G9" s="6">
-        <f>(E9+F9)/2</f>
-        <v/>
-      </c>
-      <c r="H9" s="22" t="n">
+      <c r="H9" s="13">
+        <f>(F9+G9)/2</f>
+        <v/>
+      </c>
+      <c r="I9" s="6">
+        <f>IF($C9="ToC",G9,H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="22" t="n">
         <v>6000</v>
       </c>
-      <c r="I9" s="8">
-        <f>D9*H9</f>
-        <v/>
-      </c>
-      <c r="J9" s="33">
-        <f>G9*H9/1000000</f>
-        <v/>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="8">
+        <f>E9*J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="33">
+        <f>I9*J9/1000000</f>
+        <v/>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>個人事業主のサイト用 3〜10万</t>
         </is>
@@ -12771,35 +12831,44 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>ToC</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="E10" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D10/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E10/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G10" s="22" t="n">
         <v>80000</v>
       </c>
-      <c r="G10" s="6">
-        <f>(E10+F10)/2</f>
-        <v/>
-      </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="13">
+        <f>(F10+G10)/2</f>
+        <v/>
+      </c>
+      <c r="I10" s="6">
+        <f>IF($C10="ToC",G10,H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="22" t="n">
         <v>9000</v>
       </c>
-      <c r="I10" s="8">
-        <f>D10*H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="33">
-        <f>G10*H10/1000000</f>
-        <v/>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="K10" s="8">
+        <f>E10*J10</f>
+        <v/>
+      </c>
+      <c r="L10" s="33">
+        <f>I10*J10/1000000</f>
+        <v/>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>結婚式ムービー外注 3〜10万</t>
         </is>
@@ -12816,35 +12885,44 @@
           <t>B</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>ToB</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="E11" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="E11" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D11/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F11" s="41" t="n">
+      <c r="F11" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E11/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G11" s="22" t="n">
         <v>120000</v>
       </c>
-      <c r="G11" s="6">
-        <f>(E11+F11)/2</f>
-        <v/>
-      </c>
-      <c r="H11" s="22" t="n">
+      <c r="H11" s="13">
+        <f>(F11+G11)/2</f>
+        <v/>
+      </c>
+      <c r="I11" s="6">
+        <f>IF($C11="ToC",G11,H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="22" t="n">
         <v>4000</v>
       </c>
-      <c r="I11" s="8">
-        <f>D11*H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="33">
-        <f>G11*H11/1000000</f>
-        <v/>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="K11" s="8">
+        <f>E11*J11</f>
+        <v/>
+      </c>
+      <c r="L11" s="33">
+        <f>I11*J11/1000000</f>
+        <v/>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>①の当社価格50万の1/4</t>
         </is>
@@ -12861,35 +12939,44 @@
           <t>B</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="42" t="inlineStr">
+        <is>
+          <t>ToB</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="E12" s="29" t="n">
         <v>16</v>
       </c>
-      <c r="E12" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D12/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F12" s="41" t="n">
+      <c r="F12" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E12/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G12" s="22" t="n">
         <v>180000</v>
       </c>
-      <c r="G12" s="6">
-        <f>(E12+F12)/2</f>
-        <v/>
-      </c>
-      <c r="H12" s="22" t="n">
+      <c r="H12" s="13">
+        <f>(F12+G12)/2</f>
+        <v/>
+      </c>
+      <c r="I12" s="6">
+        <f>IF($C12="ToC",G12,H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="22" t="n">
         <v>2500</v>
       </c>
-      <c r="I12" s="8">
-        <f>D12*H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="33">
-        <f>G12*H12/1000000</f>
-        <v/>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="K12" s="8">
+        <f>E12*J12</f>
+        <v/>
+      </c>
+      <c r="L12" s="33">
+        <f>I12*J12/1000000</f>
+        <v/>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>①の当社価格100万の1/5〜1/6</t>
         </is>
@@ -12906,35 +12993,44 @@
           <t>B</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="42" t="inlineStr">
+        <is>
+          <t>ToB</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="E13" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="E13" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D13/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F13" s="41" t="n">
+      <c r="F13" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E13/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G13" s="22" t="n">
         <v>150000</v>
       </c>
-      <c r="G13" s="6">
-        <f>(E13+F13)/2</f>
-        <v/>
-      </c>
-      <c r="H13" s="22" t="n">
+      <c r="H13" s="13">
+        <f>(F13+G13)/2</f>
+        <v/>
+      </c>
+      <c r="I13" s="6">
+        <f>IF($C13="ToC",G13,H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="22" t="n">
         <v>5000</v>
       </c>
-      <c r="I13" s="8">
-        <f>D13*H13</f>
-        <v/>
-      </c>
-      <c r="J13" s="33">
-        <f>G13*H13/1000000</f>
-        <v/>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K13" s="8">
+        <f>E13*J13</f>
+        <v/>
+      </c>
+      <c r="L13" s="33">
+        <f>I13*J13/1000000</f>
+        <v/>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>機能数で振れる</t>
         </is>
@@ -12951,35 +13047,44 @@
           <t>B</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="42" t="inlineStr">
+        <is>
+          <t>ToB</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="E14" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="E14" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D14/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F14" s="41" t="n">
+      <c r="F14" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E14/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G14" s="22" t="n">
         <v>100000</v>
       </c>
-      <c r="G14" s="6">
-        <f>(E14+F14)/2</f>
-        <v/>
-      </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="13">
+        <f>(F14+G14)/2</f>
+        <v/>
+      </c>
+      <c r="I14" s="6">
+        <f>IF($C14="ToC",G14,H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="22" t="n">
         <v>3500</v>
       </c>
-      <c r="I14" s="8">
-        <f>D14*H14</f>
-        <v/>
-      </c>
-      <c r="J14" s="33">
-        <f>G14*H14/1000000</f>
-        <v/>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8">
+        <f>E14*J14</f>
+        <v/>
+      </c>
+      <c r="L14" s="33">
+        <f>I14*J14/1000000</f>
+        <v/>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>撮影なし・生成のみ</t>
         </is>
@@ -12996,35 +13101,44 @@
           <t>B</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="42" t="inlineStr">
+        <is>
+          <t>ToB</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="E15" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D15/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F15" s="41" t="n">
+      <c r="F15" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E15/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G15" s="22" t="n">
         <v>80000</v>
       </c>
-      <c r="G15" s="6">
-        <f>(E15+F15)/2</f>
-        <v/>
-      </c>
-      <c r="H15" s="22" t="n">
+      <c r="H15" s="13">
+        <f>(F15+G15)/2</f>
+        <v/>
+      </c>
+      <c r="I15" s="6">
+        <f>IF($C15="ToC",G15,H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="22" t="n">
         <v>2000</v>
       </c>
-      <c r="I15" s="8">
-        <f>D15*H15</f>
-        <v/>
-      </c>
-      <c r="J15" s="33">
-        <f>G15*H15/1000000</f>
-        <v/>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K15" s="8">
+        <f>E15*J15</f>
+        <v/>
+      </c>
+      <c r="L15" s="33">
+        <f>I15*J15/1000000</f>
+        <v/>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>①の当社価格30万の1/4</t>
         </is>
@@ -13041,35 +13155,44 @@
           <t>B</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="42" t="inlineStr">
+        <is>
+          <t>ToB</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="E16" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="E16" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D16/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F16" s="41" t="n">
+      <c r="F16" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E16/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G16" s="22" t="n">
         <v>120000</v>
       </c>
-      <c r="G16" s="6">
-        <f>(E16+F16)/2</f>
-        <v/>
-      </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="13">
+        <f>(F16+G16)/2</f>
+        <v/>
+      </c>
+      <c r="I16" s="6">
+        <f>IF($C16="ToC",G16,H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="22" t="n">
         <v>6000</v>
       </c>
-      <c r="I16" s="8">
-        <f>D16*H16</f>
-        <v/>
-      </c>
-      <c r="J16" s="33">
-        <f>G16*H16/1000000</f>
-        <v/>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="8">
+        <f>E16*J16</f>
+        <v/>
+      </c>
+      <c r="L16" s="33">
+        <f>I16*J16/1000000</f>
+        <v/>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>3本セット</t>
         </is>
@@ -13086,35 +13209,44 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>ToC</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="E17" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="E17" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D17/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F17" s="41" t="n">
+      <c r="F17" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E17/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G17" s="22" t="n">
         <v>150000</v>
       </c>
-      <c r="G17" s="6">
-        <f>(E17+F17)/2</f>
-        <v/>
-      </c>
-      <c r="H17" s="22" t="n">
+      <c r="H17" s="13">
+        <f>(F17+G17)/2</f>
+        <v/>
+      </c>
+      <c r="I17" s="6">
+        <f>IF($C17="ToC",G17,H17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="22" t="n">
         <v>5900</v>
       </c>
-      <c r="I17" s="8">
-        <f>D17*H17</f>
-        <v/>
-      </c>
-      <c r="J17" s="33">
-        <f>G17*H17/1000000</f>
-        <v/>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K17" s="8">
+        <f>E17*J17</f>
+        <v/>
+      </c>
+      <c r="L17" s="33">
+        <f>I17*J17/1000000</f>
+        <v/>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>パッケージに収まらない個別要望</t>
         </is>
@@ -13131,37 +13263,46 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="42" t="inlineStr">
+        <is>
+          <t>ToB</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="E18" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="E18" s="27">
-        <f>ROUNDUP('クリエイター経済'!$B$10*D18/(1-$B$28)/500,0)*500</f>
-        <v/>
-      </c>
-      <c r="F18" s="41" t="n">
+      <c r="F18" s="27">
+        <f>ROUNDUP('クリエイター経済'!$B$10*E18/(1-$B$28)/500,0)*500</f>
+        <v/>
+      </c>
+      <c r="G18" s="22" t="n">
         <v>1000000</v>
       </c>
-      <c r="G18" s="6">
-        <f>(E18+F18)/2</f>
-        <v/>
-      </c>
-      <c r="H18" s="22" t="n">
+      <c r="H18" s="13">
+        <f>(F18+G18)/2</f>
+        <v/>
+      </c>
+      <c r="I18" s="6">
+        <f>IF($C18="ToC",G18,H18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="22" t="n">
         <v>8900</v>
       </c>
-      <c r="I18" s="8">
-        <f>D18*H18</f>
-        <v/>
-      </c>
-      <c r="J18" s="33">
-        <f>G18*H18/1000000</f>
-        <v/>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>上限100万。月742件</t>
+      <c r="K18" s="8">
+        <f>E18*J18</f>
+        <v/>
+      </c>
+      <c r="L18" s="33">
+        <f>I18*J18/1000000</f>
+        <v/>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>上限100万。交渉が入る</t>
         </is>
       </c>
     </row>
@@ -13176,16 +13317,16 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H20" s="25">
-        <f>SUMIF($B$5:$B$18,"A",H$5:H$18)</f>
-        <v/>
-      </c>
-      <c r="I20" s="25">
-        <f>SUMIF($B$5:$B$18,"A",I$5:I$18)</f>
-        <v/>
-      </c>
-      <c r="J20" s="32">
+      <c r="J20" s="25">
         <f>SUMIF($B$5:$B$18,"A",J$5:J$18)</f>
+        <v/>
+      </c>
+      <c r="K20" s="25">
+        <f>SUMIF($B$5:$B$18,"A",K$5:K$18)</f>
+        <v/>
+      </c>
+      <c r="L20" s="32">
+        <f>SUMIF($B$5:$B$18,"A",L$5:L$18)</f>
         <v/>
       </c>
     </row>
@@ -13200,16 +13341,16 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H21" s="25">
-        <f>SUMIF($B$5:$B$18,"B",H$5:H$18)</f>
-        <v/>
-      </c>
-      <c r="I21" s="25">
-        <f>SUMIF($B$5:$B$18,"B",I$5:I$18)</f>
-        <v/>
-      </c>
-      <c r="J21" s="32">
+      <c r="J21" s="25">
         <f>SUMIF($B$5:$B$18,"B",J$5:J$18)</f>
+        <v/>
+      </c>
+      <c r="K21" s="25">
+        <f>SUMIF($B$5:$B$18,"B",K$5:K$18)</f>
+        <v/>
+      </c>
+      <c r="L21" s="32">
+        <f>SUMIF($B$5:$B$18,"B",L$5:L$18)</f>
         <v/>
       </c>
     </row>
@@ -13224,16 +13365,16 @@
           <t>C</t>
         </is>
       </c>
-      <c r="H22" s="25">
-        <f>SUMIF($B$5:$B$18,"C",H$5:H$18)</f>
-        <v/>
-      </c>
-      <c r="I22" s="25">
-        <f>SUMIF($B$5:$B$18,"C",I$5:I$18)</f>
-        <v/>
-      </c>
-      <c r="J22" s="32">
+      <c r="J22" s="25">
         <f>SUMIF($B$5:$B$18,"C",J$5:J$18)</f>
+        <v/>
+      </c>
+      <c r="K22" s="25">
+        <f>SUMIF($B$5:$B$18,"C",K$5:K$18)</f>
+        <v/>
+      </c>
+      <c r="L22" s="32">
+        <f>SUMIF($B$5:$B$18,"C",L$5:L$18)</f>
         <v/>
       </c>
     </row>
@@ -13243,16 +13384,16 @@
           <t>合計（②-Cの共食い前）</t>
         </is>
       </c>
-      <c r="H23" s="6">
-        <f>SUM(H20:H22)</f>
-        <v/>
-      </c>
-      <c r="I23" s="6">
-        <f>SUM(I20:I22)</f>
-        <v/>
-      </c>
-      <c r="J23" s="35">
+      <c r="J23" s="6">
         <f>SUM(J20:J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="6">
+        <f>SUM(K20:K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="35">
+        <f>SUM(L20:L22)</f>
         <v/>
       </c>
     </row>
@@ -13262,11 +13403,11 @@
           <t xml:space="preserve">　− ②-Cセルフサーブによる共食い（③-A）</t>
         </is>
       </c>
-      <c r="J24" s="42">
-        <f>-J20*G35</f>
-        <v/>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
+      <c r="L24" s="43">
+        <f>-L20*G35</f>
+        <v/>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>③-Aの安い帯が②-Cに流れる分。下の期別GMVはこれを引いた後</t>
         </is>
@@ -13278,8 +13419,8 @@
           <t>5期GMV（共食い後）＝下の期別G列と一致</t>
         </is>
       </c>
-      <c r="J25" s="35">
-        <f>J23+J24</f>
+      <c r="L25" s="35">
+        <f>L23+L24</f>
         <v/>
       </c>
     </row>
@@ -13296,7 +13437,7 @@
           <t>手数料率</t>
         </is>
       </c>
-      <c r="B28" s="43" t="n">
+      <c r="B28" s="44" t="n">
         <v>0.3</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -13311,7 +13452,7 @@
           <t>決済手数料率</t>
         </is>
       </c>
-      <c r="B29" s="43" t="n">
+      <c r="B29" s="44" t="n">
         <v>0.0318</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
@@ -13326,7 +13467,7 @@
           <t>期別</t>
         </is>
       </c>
-      <c r="B30" s="43" t="n">
+      <c r="B30" s="44" t="n">
         <v>0.03</v>
       </c>
       <c r="K30" s="7" t="inlineStr">
@@ -13495,23 +13636,23 @@
       </c>
       <c r="B36" s="5" t="inlineStr"/>
       <c r="C36" s="27">
-        <f>$J$20*C32*(1-C35)</f>
+        <f>$L$20*C32*(1-C35)</f>
         <v/>
       </c>
       <c r="D36" s="27">
-        <f>$J$20*D32*(1-D35)</f>
+        <f>$L$20*D32*(1-D35)</f>
         <v/>
       </c>
       <c r="E36" s="27">
-        <f>$J$20*E32*(1-E35)</f>
+        <f>$L$20*E32*(1-E35)</f>
         <v/>
       </c>
       <c r="F36" s="27">
-        <f>$J$20*F32*(1-F35)</f>
+        <f>$L$20*F32*(1-F35)</f>
         <v/>
       </c>
       <c r="G36" s="27">
-        <f>$J$20*G32*(1-G35)</f>
+        <f>$L$20*G32*(1-G35)</f>
         <v/>
       </c>
     </row>
@@ -13523,23 +13664,23 @@
       </c>
       <c r="B37" s="5" t="inlineStr"/>
       <c r="C37" s="27">
-        <f>$J$21*C33</f>
+        <f>$L$21*C33</f>
         <v/>
       </c>
       <c r="D37" s="27">
-        <f>$J$21*D33</f>
+        <f>$L$21*D33</f>
         <v/>
       </c>
       <c r="E37" s="27">
-        <f>$J$21*E33</f>
+        <f>$L$21*E33</f>
         <v/>
       </c>
       <c r="F37" s="27">
-        <f>$J$21*F33</f>
+        <f>$L$21*F33</f>
         <v/>
       </c>
       <c r="G37" s="27">
-        <f>$J$21*G33</f>
+        <f>$L$21*G33</f>
         <v/>
       </c>
     </row>
@@ -13551,23 +13692,23 @@
       </c>
       <c r="B38" s="5" t="inlineStr"/>
       <c r="C38" s="27">
-        <f>$J$22*C34</f>
+        <f>$L$22*C34</f>
         <v/>
       </c>
       <c r="D38" s="27">
-        <f>$J$22*D34</f>
+        <f>$L$22*D34</f>
         <v/>
       </c>
       <c r="E38" s="27">
-        <f>$J$22*E34</f>
+        <f>$L$22*E34</f>
         <v/>
       </c>
       <c r="F38" s="27">
-        <f>$J$22*F34</f>
+        <f>$L$22*F34</f>
         <v/>
       </c>
       <c r="G38" s="27">
-        <f>$J$22*G34</f>
+        <f>$L$22*G34</f>
         <v/>
       </c>
     </row>
@@ -13607,23 +13748,23 @@
       </c>
       <c r="B40" s="5" t="inlineStr"/>
       <c r="C40" s="27">
-        <f>$H$20*C32*(1-C35)+$H$21*C33+$H$22*C34</f>
+        <f>$J$20*C32*(1-C35)+$J$21*C33+$J$22*C34</f>
         <v/>
       </c>
       <c r="D40" s="27">
-        <f>$H$20*D32*(1-D35)+$H$21*D33+$H$22*D34</f>
+        <f>$J$20*D32*(1-D35)+$J$21*D33+$J$22*D34</f>
         <v/>
       </c>
       <c r="E40" s="27">
-        <f>$H$20*E32*(1-E35)+$H$21*E33+$H$22*E34</f>
+        <f>$J$20*E32*(1-E35)+$J$21*E33+$J$22*E34</f>
         <v/>
       </c>
       <c r="F40" s="27">
-        <f>$H$20*F32*(1-F35)+$H$21*F33+$H$22*F34</f>
+        <f>$J$20*F32*(1-F35)+$J$21*F33+$J$22*F34</f>
         <v/>
       </c>
       <c r="G40" s="27">
-        <f>$H$20*G32*(1-G35)+$H$21*G33+$H$22*G34</f>
+        <f>$J$20*G32*(1-G35)+$J$21*G33+$J$22*G34</f>
         <v/>
       </c>
     </row>
@@ -13719,23 +13860,23 @@
       </c>
       <c r="B44" s="5" t="inlineStr"/>
       <c r="C44" s="27">
-        <f>$I$20*C32*(1-C35)+$I$21*C33+$I$22*C34</f>
+        <f>$K$20*C32*(1-C35)+$K$21*C33+$K$22*C34</f>
         <v/>
       </c>
       <c r="D44" s="27">
-        <f>$I$20*D32*(1-D35)+$I$21*D33+$I$22*D34</f>
+        <f>$K$20*D32*(1-D35)+$K$21*D33+$K$22*D34</f>
         <v/>
       </c>
       <c r="E44" s="27">
-        <f>$I$20*E32*(1-E35)+$I$21*E33+$I$22*E34</f>
+        <f>$K$20*E32*(1-E35)+$K$21*E33+$K$22*E34</f>
         <v/>
       </c>
       <c r="F44" s="27">
-        <f>$I$20*F32*(1-F35)+$I$21*F33+$I$22*F34</f>
+        <f>$K$20*F32*(1-F35)+$K$21*F33+$K$22*F34</f>
         <v/>
       </c>
       <c r="G44" s="27">
-        <f>$I$20*G32*(1-G35)+$I$21*G33+$I$22*G34</f>
+        <f>$K$20*G32*(1-G35)+$K$21*G33+$K$22*G34</f>
         <v/>
       </c>
     </row>
@@ -14327,19 +14468,19 @@
           <t>中国クリエイター 登録（人）</t>
         </is>
       </c>
-      <c r="C18" s="44" t="n">
+      <c r="C18" s="45" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="44" t="n">
+      <c r="D18" s="45" t="n">
         <v>120</v>
       </c>
-      <c r="E18" s="44" t="n">
+      <c r="E18" s="45" t="n">
         <v>500</v>
       </c>
-      <c r="F18" s="44" t="n">
+      <c r="F18" s="45" t="n">
         <v>1200</v>
       </c>
-      <c r="G18" s="44" t="n">
+      <c r="G18" s="45" t="n">
         <v>2000</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -14534,7 +14675,7 @@
           <t>構成比 合計</t>
         </is>
       </c>
-      <c r="C31" s="45">
+      <c r="C31" s="46">
         <f>SUM(C25:C30)</f>
         <v/>
       </c>

--- a/事業計画_Ver0.8.xlsx
+++ b/事業計画_Ver0.8.xlsx
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>③を中点成約に／②に解約率</t>
+          <t>③をToC上限・ToB中点に／②に解約率</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>上限成約→中点成約。GMVは約57%に</t>
+          <t>ToC＝上限／ToB＝中点。GMVは約64%に</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>★法人10%・個人40%の年次解約率を新設</t>
+          <t>★法人5%・個人30%の年次解約率を新設</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7423,12 @@
       <c r="B29" s="57" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>② に解約率を新設（★法人・個人とも 年30%）</t>
+          <t>② に解約率を新設（★法人 年5%／個人 年30%）</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>契約数は「新規獲得−解約」の純増に。法人600→481社、個人17,000→14,180人。②売上 41.6億→34.3億</t>
+          <t>契約数は「新規獲得−解約」の純増に。法人600→578社、個人17,000→14,180人。②売上 41.6億→37.5億</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>制作会社チャネル＝法人契約数×転換率なので、①の本数 3,780→3,679本、売上 35.7→34.8億</t>
+          <t>制作会社チャネル＝法人契約数×転換率なので、①の本数 3,780→3,727本、売上 35.7→35.2億</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>5期 売上 120.0→94.9億、営業利益 45.4→26.4億（37.8%→27.8%）。黒字化は3期のまま。2期末キャッシュ198百万でシリーズA前の資金ショートなし</t>
+          <t>5期 売上 120.0→100.2億、営業利益 45.4→29.5億（37.8%→29.4%）。黒字化は3期のまま。2期末キャッシュ198百万でシリーズA前の資金ショートなし</t>
         </is>
       </c>
     </row>
@@ -11628,20 +11628,20 @@
         <v>0</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>★年30%（松田さん指示）。B2B SaaSの一般水準（5〜15%）より高く、保守側に置いている</t>
+          <t>★年5%（松田さん指示）。B2B SaaSの一般水準（5〜15%）の下限</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>★年30%（松田さん指示）。個人向けSaaSとしてはむしろ低め。法人と同率で置いている</t>
+          <t>★年30%（松田さん指示）。個人向けSaaSの一般水準（月3〜5%＝年30〜45%）の下限側</t>
         </is>
       </c>
     </row>

--- a/事業計画_Ver0.8.xlsx
+++ b/事業計画_Ver0.8.xlsx
@@ -12429,7 +12429,7 @@
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>★ 解約率を入れたので、契約数は「新規獲得 − 解約」の純増になる。5期に法人600社を維持するには、累計600社ではなく解約分を上乗せして獲得し続ける必要がある。</t>
+          <t>★ 解約率を入れたので、契約数は「新規獲得 − 解約」の純増になる。累計獲得は法人600社・個人17,000人だが、解約を引いた5期末は法人578社・個人14,180人。差の22社・2,820人は、維持するなら解約分を上乗せして獲得し続ける必要がある。</t>
         </is>
       </c>
     </row>

--- a/事業計画_Ver0.8.xlsx
+++ b/事業計画_Ver0.8.xlsx
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>③をToC上限・ToB中点に／②に解約率</t>
+          <t>②に解約率／費用5項目を追加。③は上限成約のまま</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>ToC＝上限／ToB＝中点。GMVは約64%に</t>
+          <t>変更なし。ToC・ToBとも上限成約を採用</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>③ 価格を ToC＝上限／ToB＝中点 に分ける</t>
+          <t>③ 価格は ToC・ToB とも上限成約（松田さん指示）</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>ToC（個人向け6商品＋個人オーダー）は定価で交渉が入らない。ToB（中小企業6商品＋企業オーダー）は相見積もりと交渉が入るので上限に張り付かない。5期GMV 142.5億→91.8億</t>
+          <t>一度は中点成約に下げ、次に ToC だけ上限に戻したが、ToB を中点に置くと採用価格が下がるため全商品で上限を採用する。5期GMV 142.5億（Ver0.7と同じ）。区分列は買い手の違いを示すために残す</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>5期 売上 120.0→100.2億、営業利益 45.4→29.5億（37.8%→29.4%）。黒字化は3期のまま。2期末キャッシュ198百万でシリーズA前の資金ショートなし</t>
+          <t>5期 売上 120.0→115.4億、営業利益 45.4→40.8億（37.8%→35.3%）。減少分は②の解約と追加費用。黒字化は3期のまま。2期末キャッシュ208百万でシリーズA前の資金ショートなし</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12479,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ToC（個人向け）は上限＝定価で成約。ToB（中小企業・企業オーダー）は交渉が入るので中点で成約。下限はクリエイターの留保価格で、下回ると供給が付かないという床。</t>
+          <t>ToC・ToBとも上限＝需要側の支払意思で成約。区分は買い手の違いを示すためだけに残している。下限はクリエイターの留保価格で、下回ると供給が付かないという床。</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
         <v/>
       </c>
       <c r="I5" s="6">
-        <f>IF($C5="ToC",G5,H5)</f>
+        <f>G5</f>
         <v/>
       </c>
       <c r="J5" s="22" t="n">
@@ -12638,7 +12638,7 @@
         <v/>
       </c>
       <c r="I6" s="6">
-        <f>IF($C6="ToC",G6,H6)</f>
+        <f>G6</f>
         <v/>
       </c>
       <c r="J6" s="22" t="n">
@@ -12692,7 +12692,7 @@
         <v/>
       </c>
       <c r="I7" s="6">
-        <f>IF($C7="ToC",G7,H7)</f>
+        <f>G7</f>
         <v/>
       </c>
       <c r="J7" s="22" t="n">
@@ -12746,7 +12746,7 @@
         <v/>
       </c>
       <c r="I8" s="6">
-        <f>IF($C8="ToC",G8,H8)</f>
+        <f>G8</f>
         <v/>
       </c>
       <c r="J8" s="22" t="n">
@@ -12800,7 +12800,7 @@
         <v/>
       </c>
       <c r="I9" s="6">
-        <f>IF($C9="ToC",G9,H9)</f>
+        <f>G9</f>
         <v/>
       </c>
       <c r="J9" s="22" t="n">
@@ -12854,7 +12854,7 @@
         <v/>
       </c>
       <c r="I10" s="6">
-        <f>IF($C10="ToC",G10,H10)</f>
+        <f>G10</f>
         <v/>
       </c>
       <c r="J10" s="22" t="n">
@@ -12908,7 +12908,7 @@
         <v/>
       </c>
       <c r="I11" s="6">
-        <f>IF($C11="ToC",G11,H11)</f>
+        <f>G11</f>
         <v/>
       </c>
       <c r="J11" s="22" t="n">
@@ -12962,7 +12962,7 @@
         <v/>
       </c>
       <c r="I12" s="6">
-        <f>IF($C12="ToC",G12,H12)</f>
+        <f>G12</f>
         <v/>
       </c>
       <c r="J12" s="22" t="n">
@@ -13016,7 +13016,7 @@
         <v/>
       </c>
       <c r="I13" s="6">
-        <f>IF($C13="ToC",G13,H13)</f>
+        <f>G13</f>
         <v/>
       </c>
       <c r="J13" s="22" t="n">
@@ -13070,7 +13070,7 @@
         <v/>
       </c>
       <c r="I14" s="6">
-        <f>IF($C14="ToC",G14,H14)</f>
+        <f>G14</f>
         <v/>
       </c>
       <c r="J14" s="22" t="n">
@@ -13124,7 +13124,7 @@
         <v/>
       </c>
       <c r="I15" s="6">
-        <f>IF($C15="ToC",G15,H15)</f>
+        <f>G15</f>
         <v/>
       </c>
       <c r="J15" s="22" t="n">
@@ -13178,7 +13178,7 @@
         <v/>
       </c>
       <c r="I16" s="6">
-        <f>IF($C16="ToC",G16,H16)</f>
+        <f>G16</f>
         <v/>
       </c>
       <c r="J16" s="22" t="n">
@@ -13232,7 +13232,7 @@
         <v/>
       </c>
       <c r="I17" s="6">
-        <f>IF($C17="ToC",G17,H17)</f>
+        <f>G17</f>
         <v/>
       </c>
       <c r="J17" s="22" t="n">
@@ -13286,7 +13286,7 @@
         <v/>
       </c>
       <c r="I18" s="6">
-        <f>IF($C18="ToC",G18,H18)</f>
+        <f>G18</f>
         <v/>
       </c>
       <c r="J18" s="22" t="n">

--- a/事業計画_Ver0.8.xlsx
+++ b/事業計画_Ver0.8.xlsx
@@ -1787,14 +1787,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>③は成約が価格帯のどこに落ちるかで3倍動く。いまは中点（均等）を採用している。</t>
+          <t>③は成約が価格帯のどこに落ちるかで約6倍動く。いまは上限（需要側の支払意思）を採用している。</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>⚠ xlsx を手で編集しないこと。make_xlsx15.py を直して再生成する。</t>
+          <t>⚠ xlsx を手で編集しないこと。make_xlsx.py を直して再生成する。</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="B20" s="49" t="inlineStr">
         <is>
-          <t>均等（価格帯の中点）</t>
+          <t>上限（需要側の支払意思）</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>下限寄りに寄ると③は1/3になる</t>
+          <t>中点なら約59%、下限寄りなら約18%まで落ちる</t>
         </is>
       </c>
     </row>
@@ -6084,46 +6084,46 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="54" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>② 解約率</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>法人 年5%／個人 年30%</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>決定</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>法人はB2B SaaS一般水準5〜15%の下限。個人は月3〜5%の下限側</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="54" t="inlineStr">
         <is>
           <t>── ★私が置いた値 ──</t>
         </is>
       </c>
-      <c r="B23" s="49" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>AX倍率</t>
-        </is>
-      </c>
-      <c r="B24" s="49" t="inlineStr">
-        <is>
-          <t>1.0 → 4.0倍</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>未実証。最重要前提。3倍でも営業利益率は成立する</t>
-        </is>
-      </c>
+      <c r="B24" s="49" t="inlineStr"/>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>① 商品の値引率</t>
+          <t>AX倍率</t>
         </is>
       </c>
       <c r="B25" s="49" t="inlineStr">
         <is>
-          <t>一律50%</t>
+          <t>1.0 → 4.0倍</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -6133,19 +6133,19 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>企業の現行支払の半額。顧客が浮かせる額が提案の中身</t>
+          <t>未実証。最重要前提。3倍でも営業利益率は成立する</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>① 難度係数</t>
+          <t>① 商品の値引率</t>
         </is>
       </c>
       <c r="B26" s="49" t="inlineStr">
         <is>
-          <t>3.0 / 1.8 / 1.0 / 0.8</t>
+          <t>一律50%</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -6155,19 +6155,19 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>商品構成比から平均難度を導出している</t>
+          <t>企業の現行支払の半額。顧客が浮かせる額が提案の中身</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>① 商品構成比</t>
+          <t>① 難度係数</t>
         </is>
       </c>
       <c r="B27" s="49" t="inlineStr">
         <is>
-          <t>年を追って上位帯へシフト</t>
+          <t>3.0 / 1.8 / 1.0 / 0.8</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -6177,19 +6177,19 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>事例が溜まるほど上の帯が取れる前提</t>
+          <t>商品構成比から平均難度を導出している</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>① 営業の担当社数・リピート</t>
+          <t>① 商品構成比</t>
         </is>
       </c>
       <c r="B28" s="49" t="inlineStr">
         <is>
-          <t>40社／年6本</t>
+          <t>年を追って上位帯へシフト</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -6199,19 +6199,19 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>エンタープライズ営業の標準的な水準</t>
+          <t>事例が溜まるほど上の帯が取れる前提</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>② SKU単価・席数・Ent比率</t>
+          <t>① 営業の担当社数・リピート</t>
         </is>
       </c>
       <c r="B29" s="49" t="inlineStr">
         <is>
-          <t>商品マスタ② 参照</t>
+          <t>40社／年6本</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -6221,19 +6221,19 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>チェックポイントに重い値付け</t>
+          <t>エンタープライズ営業の標準的な水準</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>③ 工数・上限価格・件数</t>
+          <t>② SKU単価・席数・Ent比率</t>
         </is>
       </c>
       <c r="B30" s="49" t="inlineStr">
         <is>
-          <t>商品マスタ③ 参照</t>
+          <t>商品マスタ② 参照</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -6243,19 +6243,19 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>上限は日本の支払意思。実測ではない</t>
+          <t>チェックポイントに重い値付け</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>③ システム原価の内訳</t>
+          <t>③ 工数・上限価格・件数</t>
         </is>
       </c>
       <c r="B31" s="49" t="inlineStr">
         <is>
-          <t>尺・保管期間・トークン数</t>
+          <t>商品マスタ③ 参照</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -6265,103 +6265,257 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>単価は公表値、使用量は仮置き</t>
+          <t>上限は日本の支払意思。実測ではない</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>③ システム原価の内訳</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="inlineStr">
+        <is>
+          <t>尺・保管期間・トークン数</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>単価は公表値、使用量は仮置き</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>希薄化係数</t>
         </is>
       </c>
-      <c r="B32" s="49" t="inlineStr">
+      <c r="B33" s="49" t="inlineStr">
         <is>
           <t>資本構成の推移 参照</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>シリーズA post 15億は未交渉</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="54" t="inlineStr">
-        <is>
-          <t>── 未確定 ──</t>
-        </is>
-      </c>
-      <c r="B33" s="49" t="inlineStr"/>
-      <c r="C33" s="20" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>中国の映像制作パートナー</t>
+          <t>貸倒引当率</t>
         </is>
       </c>
       <c r="B34" s="49" t="inlineStr">
         <is>
-          <t>社名 ［記入予定］</t>
+          <t>売上の0.5%</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>未確定</t>
+          <t>★</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>契約前。権利は日本側に帰属する設計</t>
+          <t>0.5〜1%の下限。貸倒が立つのは①の掛売のみ（③は収納代行・②は前受）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>パートナーの取り分</t>
+          <t>採用費率</t>
         </is>
       </c>
       <c r="B35" s="49" t="inlineStr">
         <is>
-          <t>30%側か70%側か</t>
+          <t>想定年収の30%</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>未確定</t>
+          <t>★</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>契約で決まる。利益に直結する</t>
+          <t>4人目から計上。最初の3名は確保済み／リファラル前提</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>監査法人費用</t>
+        </is>
+      </c>
+      <c r="B36" s="49" t="inlineStr">
+        <is>
+          <t>3期から 年2,000万</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>N-2期から。その他販管費の見積からは監査報酬を外している</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>上場関連費用</t>
+        </is>
+      </c>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>上場期に 1億</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>主幹事・印刷・株式事務。5期に一括計上</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>知財関連費</t>
+        </is>
+      </c>
+      <c r="B38" s="49" t="inlineStr">
+        <is>
+          <t>1期300万／2期以降 売上の0.5%</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>出願・維持・侵害監視。件数ではなく売上比で置いている</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>為替ヘッジ付保率</t>
+        </is>
+      </c>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>外貨支払見込みの50%</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>3〜6ヶ月の為替予約。残高が薄い1〜2期は付保率を下げる</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="54" t="inlineStr">
+        <is>
+          <t>── 未確定 ──</t>
+        </is>
+      </c>
+      <c r="B40" s="49" t="inlineStr"/>
+      <c r="C40" s="20" t="inlineStr"/>
+      <c r="D40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>中国の映像制作パートナー</t>
+        </is>
+      </c>
+      <c r="B41" s="49" t="inlineStr">
+        <is>
+          <t>社名 ［記入予定］</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>契約前。権利は日本側に帰属する設計</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>パートナーの取り分</t>
+        </is>
+      </c>
+      <c r="B42" s="49" t="inlineStr">
+        <is>
+          <t>30%側か70%側か</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>契約で決まる。利益に直結する</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
           <t>業務委託の契約設計</t>
         </is>
       </c>
-      <c r="B36" s="49" t="inlineStr">
+      <c r="B43" s="49" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>偽装請負と読まれない設計。1年目に弁護士と</t>
         </is>
@@ -7526,7 +7680,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>外貨建て支払は5期10.3億。10%円安で1.0億の利益圧迫。ヘッジは外貨支払見込みの50%★を予約</t>
+          <t>外貨建て支払は5期12.2億。10%円安で1.2億の利益圧迫。ヘッジは外貨支払見込みの50%★を予約</t>
         </is>
       </c>
     </row>
@@ -7547,14 +7701,14 @@
     <row r="39">
       <c r="A39" s="39" t="inlineStr">
         <is>
-          <t>⚠ 0.4 → 0.5 は構造の作り直し、0.5 → 0.6 は前提を実勢データで詰めたもの、0.7 は③-Cの件数を落として120億に合わせ、0.8 は知財を明示して前提を保守化したもの。5期の売上は 88.1億 → 130.3億 → 120.0億、社員は 61名 → 22名。数字が良くなった分だけ、前提の説明責任が重くなっている。</t>
+          <t>⚠ 0.4 → 0.5 は構造の作り直し、0.5 → 0.6 は前提を実勢データで詰めたもの、0.7 は③-Cの件数を落として120億に合わせ、0.8 は知財を明示して前提を保守化したもの。5期の売上は 88.1億 → 130.3億 → 120.0億 → 115.4億、社員は 61名 → 22名。数字が良くなった分だけ、前提の説明責任が重くなっている。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="39" t="inlineStr">
         <is>
-          <t>⚠ PPTX「投資家向け企画書 Ver1.4.pptx」はまだ旧番号のまま。改番するかは松田さんの指示待ち。</t>
+          <t>PPTX「投資家向け企画書 Ver0.8.pptx」は本シートと同じ数値で再生成済み。deck/build.js を直して node build.js → slim.py の順で作る。</t>
         </is>
       </c>
     </row>
@@ -13883,7 +14037,7 @@
     <row r="46">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>⚠ 全商品が上限で成約する前提。下限（クリエイターの留保価格）との差がそのまま利幅になる。供給が厚いほど競争で下限側に寄るのが市場の常なので、ここは最も強気の置き方。中点なら③のGMVは約57%、全部が下限なら約5%になる。</t>
+          <t>⚠ 全商品が上限で成約する前提。下限（クリエイターの留保価格）との差がそのまま利幅になる。供給が厚いほど競争で下限側に寄るのが市場の常なので、ここは最も強気の置き方。中点なら③のGMVは上限の約59%、全部が下限なら約18%になる。</t>
         </is>
       </c>
     </row>

--- a/事業計画_Ver0.8.xlsx
+++ b/事業計画_Ver0.8.xlsx
@@ -14406,7 +14406,7 @@
         <v>550</v>
       </c>
       <c r="C9" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="22" t="n">
         <v>1</v>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>AX化で極小。取引処理はBPO、専門領域は社外の顧問</t>
+          <t>AX化で極小。取引処理はBPO、専門領域は社外の顧問。1期から1名（設立・調達・契約の実務）</t>
         </is>
       </c>
     </row>

--- a/事業計画_Ver0.8.xlsx
+++ b/事業計画_Ver0.8.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>★法人5%・個人30%の年次解約率を新設</t>
+          <t>★法人5%・個人30%の解約率を新設／Standardを5席に</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7689,24 +7689,52 @@
       <c r="B37" s="57" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
+          <t>1期の社員を5名→6名（松田さん指示）</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>管理・コーポレートを1期から1名置く。設立・調達・業務委託契約の実務が初年度から発生するため。1期人件費 44.1→50.5百万、1期末キャッシュ 45→37百万（月次バーン950万で4ヶ月分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr"/>
+      <c r="B38" s="57" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>②Standard の席数を 3→5（松田さん指示）</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>席単価24万は据え置き。Standard年額 196→244万で1席48.8万となり、Enterprise 56.4万/席との逆転が解消。5期②売上 37.5→39.4億</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr"/>
+      <c r="B39" s="57" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
           <t>再計算の結果</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>5期 売上 120.0→115.4億、営業利益 45.4→40.8億（37.8%→35.3%）。減少分は②の解約と追加費用。黒字化は3期のまま。2期末キャッシュ208百万でシリーズA前の資金ショートなし</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>5期 売上 120.0→117.4億、営業利益 45.4→41.9億（37.8%→35.7%）。減少分は②の解約と追加費用。黒字化は3期のまま。2期末キャッシュ209百万でシリーズA前の資金ショートなし</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
         <is>
           <t>⚠ 0.4 → 0.5 は構造の作り直し、0.5 → 0.6 は前提を実勢データで詰めたもの、0.7 は③-Cの件数を落として120億に合わせ、0.8 は知財を明示して前提を保守化したもの。5期の売上は 88.1億 → 130.3億 → 120.0億 → 115.4億、社員は 61名 → 22名。数字が良くなった分だけ、前提の説明責任が重くなっている。</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="39" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="39" t="inlineStr">
         <is>
           <t>PPTX「投資家向け企画書 Ver0.8.pptx」は本シートと同じ数値で再生成済み。deck/build.js を直して node build.js → slim.py の順で作る。</t>
         </is>
@@ -11674,7 +11702,7 @@
         <v/>
       </c>
       <c r="F13" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">

--- a/事業計画_Ver0.8.xlsx
+++ b/事業計画_Ver0.8.xlsx
@@ -7129,7 +7129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7717,24 +7717,38 @@
       <c r="B39" s="57" t="inlineStr"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
+          <t>管理・コーポレート3名の内訳と職務分掌を明記（数値は変更なし）</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>経理1・法務1・内部監査1（専任・独立）。承認はCFO。作業量はAXとBPOで圧縮できるが、独立性・職務分掌・内部統制報告書の責任者は圧縮できない。「3名では薄い」への回答をシートに持たせた</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr"/>
+      <c r="B40" s="57" t="inlineStr"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
           <t>再計算の結果</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>5期 売上 120.0→117.4億、営業利益 45.4→41.9億（37.8%→35.7%）。減少分は②の解約と追加費用。黒字化は3期のまま。2期末キャッシュ209百万でシリーズA前の資金ショートなし</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="39" t="inlineStr">
-        <is>
-          <t>⚠ 0.4 → 0.5 は構造の作り直し、0.5 → 0.6 は前提を実勢データで詰めたもの、0.7 は③-Cの件数を落として120億に合わせ、0.8 は知財を明示して前提を保守化したもの。5期の売上は 88.1億 → 130.3億 → 120.0億 → 115.4億、社員は 61名 → 22名。数字が良くなった分だけ、前提の説明責任が重くなっている。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t>⚠ 0.4 → 0.5 は構造の作り直し、0.5 → 0.6 は前提を実勢データで詰めたもの、0.7 は③-Cの件数を落として120億に合わせ、0.8 は知財を明示して前提を保守化したもの。5期の売上は 88.1億 → 130.3億 → 120.0億 → 115.4億、社員は 61名 → 22名。数字が良くなった分だけ、前提の説明責任が重くなっている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
         <is>
           <t>PPTX「投資家向け企画書 Ver0.8.pptx」は本シートと同じ数値で再生成済み。deck/build.js を直して node build.js → slim.py の順で作る。</t>
         </is>
@@ -14200,7 +14214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -15102,7 +15116,7 @@
     <row r="45">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>⚠ 管理・コーポレート3名は、5期に上場会社として内部統制報告制度の対象になる規模には薄い。取引処理はBPOに出す前提だが、内部統制の設計・運用・評価は社員の仕事。監査法人と主幹事に早期に当てること。★確認事項</t>
+          <t>⚠ 管理・コーポレート3名は「作業量が3人分」ではなく「独立性と職務分掌が成立する最小構成」。記帳・支払・消込はBPOと自動化に出す前提で、人数はAXで減らせる。減らせないのは下表の3つ（独立性・分掌・責任者）。内訳は73行目以降。</t>
         </is>
       </c>
     </row>
@@ -15160,7 +15174,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>上場会社・売上108億規模</t>
+          <t>上場会社・売上117億規模</t>
         </is>
       </c>
     </row>
@@ -15587,6 +15601,172 @@
         <v/>
       </c>
       <c r="H71" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>管理・コーポレート3名の内訳と職務分掌</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>「3名では薄い」と言われたときに出す表。人数ではなく、誰が何を担い、誰が承認するかで答える。作業量はAXとBPOで圧縮できるが、独立性・職務分掌・責任者はできない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>担う業務</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>承認・チェックは誰が／外にいる専門家</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>経理・決算・開示</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>月次・四半期・年次決算、開示書類、税務、資金繰り、外貨と為替予約</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>承認は CFO（経営・CxO 3名に含む）。記帳・支払・消込はBPO。税務は税理士</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>法務・コンプライアンス</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>業務委託契約（制作28名・開発19名・クリエイター681名稼働）、資金決済法、中国パートナー、知財の帰属</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>顧問弁護士（5期30百万）。契約審査は外、運用は社内</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>内部監査（専任・独立）</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>J-SOXの運用評価、委託先の往査、③の資金受払（年95,200件）の統制テスト</t>
+        </is>
+      </c>
+      <c r="H78" s="38" t="inlineStr">
+        <is>
+          <t>★ここは兼任できない。統制を運用する人と評価する人は別人でなければならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B79" s="6">
+        <f>SUM(B76:B78)</f>
+        <v/>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>実働は2名。3名のうち1名は内部監査に取られる</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="39" t="inlineStr">
+        <is>
+          <t>⚠ AXで消せないもの — 人数を増やしても能力を上げても解けない種類の制約</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>内部監査の独立性</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>1人が10人分の処理能力を持っていても、自分で自分を監査できない。評価者は運用者と別人</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>職務分掌（起票と承認の分離）</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>管理が1名だと支払の起票も承認も同じ人になる。能力ではなく構造の欠陥として指摘される</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>内部統制報告書の責任者</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>署名する人が社内に要る。外注できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="39" t="inlineStr">
+        <is>
+          <t>⚠ 逆に、3名で回る根拠はBPOと外部専門家。その費用が上の47行目以降で見えていること。BPO（5期10億）に記帳・支払・消込が含まれる前提だが、シート上のラベルは「CS・運用」のまま。★内訳の明示は未了</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
